--- a/public/sample-pre.xlsx
+++ b/public/sample-pre.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="回答" sheetId="1" r:id="rId1"/>
+    <sheet name="フォームの回答 1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,271 +397,511 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AO4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>氏名</v>
+        <v>タイムスタンプ</v>
       </c>
       <c r="B1" t="str">
-        <v>メール</v>
+        <v>メールアドレス</v>
       </c>
       <c r="C1" t="str">
-        <v>所属</v>
+        <v>お名前</v>
       </c>
       <c r="D1" t="str">
-        <v>B1</v>
+        <v>1. ストレスチェック設問1</v>
       </c>
       <c r="E1" t="str">
-        <v>B2</v>
+        <v>2. ストレスチェック設問2</v>
       </c>
       <c r="F1" t="str">
-        <v>B3</v>
+        <v>3. ストレスチェック設問3</v>
       </c>
       <c r="G1" t="str">
-        <v>B4</v>
+        <v>4. ストレスチェック設問4</v>
       </c>
       <c r="H1" t="str">
-        <v>T1</v>
+        <v>5. ストレスチェック設問5</v>
       </c>
       <c r="I1" t="str">
-        <v>T2</v>
+        <v>6. ストレスチェック設問6</v>
       </c>
       <c r="J1" t="str">
-        <v>T3</v>
+        <v>7. ストレスチェック設問7</v>
       </c>
       <c r="K1" t="str">
-        <v>T4</v>
+        <v>8. ストレスチェック設問8</v>
       </c>
       <c r="L1" t="str">
-        <v>R1</v>
+        <v>9. ストレスチェック設問9</v>
       </c>
       <c r="M1" t="str">
-        <v>R2</v>
+        <v>10. ストレスチェック設問10</v>
       </c>
       <c r="N1" t="str">
-        <v>R3</v>
+        <v>11. ストレスチェック設問11</v>
       </c>
       <c r="O1" t="str">
-        <v>R4</v>
+        <v>12. ストレスチェック設問12</v>
       </c>
       <c r="P1" t="str">
-        <v>C1</v>
+        <v>13. ストレスチェック設問13</v>
       </c>
       <c r="Q1" t="str">
-        <v>C2</v>
+        <v>14. ストレスチェック設問14</v>
       </c>
       <c r="R1" t="str">
-        <v>C3</v>
+        <v>15. ストレスチェック設問15</v>
       </c>
       <c r="S1" t="str">
-        <v>C4</v>
+        <v>16. ストレスチェック設問16</v>
       </c>
       <c r="T1" t="str">
-        <v>A1</v>
+        <v>17. ストレスチェック設問17</v>
       </c>
       <c r="U1" t="str">
-        <v>A2</v>
+        <v>18. ストレスチェック設問18</v>
+      </c>
+      <c r="V1" t="str">
+        <v>1. コンピテンシー設問1</v>
+      </c>
+      <c r="W1" t="str">
+        <v>2. コンピテンシー設問2</v>
+      </c>
+      <c r="X1" t="str">
+        <v>3. コンピテンシー設問3</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>4. コンピテンシー設問4</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>5. コンピテンシー設問5</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>6. コンピテンシー設問6</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>7. コンピテンシー設問7</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>8. コンピテンシー設問8</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>9. コンピテンシー設問9</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>10. コンピテンシー設問10</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>11. コンピテンシー設問11</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>12. コンピテンシー設問12</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>13. コンピテンシー設問13</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>14. コンピテンシー設問14</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>15. コンピテンシー設問15</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>16. コンピテンシー設問16</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>17. コンピテンシー設問17</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>18. コンピテンシー設問18</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>19. コンピテンシー設問19</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>20. コンピテンシー設問20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>2026-04-05 09:00:00</v>
+      </c>
+      <c r="B2" t="str">
+        <v>山田 太郎@example.com</v>
+      </c>
+      <c r="C2" t="str">
         <v>山田 太郎</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N2">
         <v>3</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q2">
         <v>3</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>3</v>
       </c>
       <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2">
+        <v>4</v>
+      </c>
+      <c r="X2">
+        <v>5</v>
+      </c>
+      <c r="Y2">
+        <v>3</v>
+      </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
+      <c r="AA2">
+        <v>5</v>
+      </c>
+      <c r="AB2">
+        <v>3</v>
+      </c>
+      <c r="AC2">
+        <v>4</v>
+      </c>
+      <c r="AD2">
+        <v>5</v>
+      </c>
+      <c r="AE2">
+        <v>3</v>
+      </c>
+      <c r="AF2">
+        <v>4</v>
+      </c>
+      <c r="AG2">
+        <v>5</v>
+      </c>
+      <c r="AH2">
+        <v>3</v>
+      </c>
+      <c r="AI2">
+        <v>4</v>
+      </c>
+      <c r="AJ2">
+        <v>5</v>
+      </c>
+      <c r="AK2">
+        <v>3</v>
+      </c>
+      <c r="AL2">
+        <v>4</v>
+      </c>
+      <c r="AM2">
+        <v>5</v>
+      </c>
+      <c r="AN2">
+        <v>3</v>
+      </c>
+      <c r="AO2">
         <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>2026-04-05 09:00:00</v>
+      </c>
+      <c r="B3" t="str">
+        <v>佐藤 花子@example.com</v>
+      </c>
+      <c r="C3" t="str">
         <v>佐藤 花子</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
       <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
+        <v>3</v>
+      </c>
+      <c r="R3">
+        <v>3</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3">
+        <v>4</v>
+      </c>
+      <c r="W3">
+        <v>5</v>
+      </c>
+      <c r="X3">
         <v>6</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
+      <c r="Y3">
+        <v>4</v>
+      </c>
+      <c r="Z3">
+        <v>5</v>
+      </c>
+      <c r="AA3">
         <v>6</v>
       </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
+      <c r="AB3">
+        <v>4</v>
+      </c>
+      <c r="AC3">
+        <v>5</v>
+      </c>
+      <c r="AD3">
         <v>6</v>
       </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
+      <c r="AE3">
+        <v>4</v>
+      </c>
+      <c r="AF3">
+        <v>5</v>
+      </c>
+      <c r="AG3">
         <v>6</v>
       </c>
-      <c r="N3">
-        <v>4</v>
-      </c>
-      <c r="O3">
-        <v>5</v>
-      </c>
-      <c r="P3">
+      <c r="AH3">
+        <v>4</v>
+      </c>
+      <c r="AI3">
+        <v>5</v>
+      </c>
+      <c r="AJ3">
         <v>6</v>
       </c>
-      <c r="Q3">
-        <v>4</v>
-      </c>
-      <c r="R3">
-        <v>5</v>
-      </c>
-      <c r="S3">
+      <c r="AK3">
+        <v>4</v>
+      </c>
+      <c r="AL3">
+        <v>5</v>
+      </c>
+      <c r="AM3">
         <v>6</v>
       </c>
-      <c r="T3">
-        <v>4</v>
-      </c>
-      <c r="U3">
+      <c r="AN3">
+        <v>4</v>
+      </c>
+      <c r="AO3">
         <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>2026-04-05 09:00:00</v>
+      </c>
+      <c r="B4" t="str">
+        <v>鈴木 一郎@example.com</v>
+      </c>
+      <c r="C4" t="str">
         <v>鈴木 一郎</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>3</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4">
+        <v>4</v>
+      </c>
+      <c r="Y4">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
+      <c r="Z4">
+        <v>3</v>
+      </c>
+      <c r="AA4">
+        <v>4</v>
+      </c>
+      <c r="AB4">
         <v>2</v>
       </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4">
+      <c r="AC4">
+        <v>3</v>
+      </c>
+      <c r="AD4">
+        <v>4</v>
+      </c>
+      <c r="AE4">
         <v>2</v>
       </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
-      </c>
-      <c r="N4">
+      <c r="AF4">
+        <v>3</v>
+      </c>
+      <c r="AG4">
+        <v>4</v>
+      </c>
+      <c r="AH4">
         <v>2</v>
       </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
-      <c r="P4">
-        <v>4</v>
-      </c>
-      <c r="Q4">
+      <c r="AI4">
+        <v>3</v>
+      </c>
+      <c r="AJ4">
+        <v>4</v>
+      </c>
+      <c r="AK4">
         <v>2</v>
       </c>
-      <c r="R4">
-        <v>3</v>
-      </c>
-      <c r="S4">
-        <v>4</v>
-      </c>
-      <c r="T4">
+      <c r="AL4">
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <v>4</v>
+      </c>
+      <c r="AN4">
         <v>2</v>
       </c>
-      <c r="U4">
+      <c r="AO4">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AO4"/>
   </ignoredErrors>
 </worksheet>
 </file>